--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -10454,12 +10454,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -10626,12 +10626,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -11486,12 +11486,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -11830,12 +11830,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11916,12 +11916,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -12604,12 +12604,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -12776,12 +12776,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -12862,12 +12862,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -13034,12 +13034,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>Padova</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Padova</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">

--- a/Dataset_combinato_GPS_finale.xlsx
+++ b/Dataset_combinato_GPS_finale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riki/U17/REPORT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131E7C34-6B03-074B-AE25-0D15A3D3D8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AE50D8-B4BD-2543-BF6C-77C0D1D3C5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,7 +276,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -333,7 +333,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
